--- a/outputs/daily/hr_rankings_2026-10-14_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-14_full.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56</v>
+        <v>58.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,14 +821,14 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>5</t>
@@ -846,12 +846,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -996,8 +996,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1011,12 +1019,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1036,12 +1044,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1068,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,40 +1082,40 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1122,12 +1130,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1149,22 +1157,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1174,72 +1182,72 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1272,8 +1280,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1287,12 +1303,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1312,12 +1328,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1352,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>54.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,40 +1366,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1398,12 +1414,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1425,22 +1441,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1450,72 +1466,72 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1548,8 +1564,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1563,12 +1587,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1588,12 +1612,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1612,7 +1636,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.1</v>
+        <v>50.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,40 +1650,40 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1674,12 +1698,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1701,22 +1725,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1731,67 +1755,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1824,8 +1848,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1839,12 +1871,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,12 +1896,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1920,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,40 +1934,40 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1950,12 +1982,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1977,27 +2009,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,67 +2039,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2100,8 +2132,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2115,12 +2155,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2140,12 +2180,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2164,7 +2204,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.1</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,40 +2218,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2226,12 +2266,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2258,22 +2298,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,67 +2323,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2376,8 +2416,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2416,7 +2464,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2488,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>46.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2464,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
         <v>88.7</v>
@@ -2652,8 +2700,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2667,24 +2723,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -2692,22 +2748,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2716,7 +2772,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.8</v>
+        <v>46.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,40 +2786,40 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2778,12 +2834,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2805,12 +2861,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2820,12 +2876,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,101 +2891,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2943,24 +3007,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -2968,22 +3032,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2992,7 +3056,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.8</v>
+        <v>43.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,26 +3070,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>33.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3039,7 +3103,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3081,12 +3145,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3096,12 +3160,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,101 +3175,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3244,7 +3316,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3340,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.2</v>
+        <v>42.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3292,7 +3364,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
         <v>92.09999999999999</v>
@@ -3480,8 +3552,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3520,7 +3600,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3624,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3568,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
         <v>90.40000000000001</v>
@@ -3756,8 +3836,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3796,7 +3884,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3908,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>40.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3844,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
         <v>95.5</v>
@@ -4032,8 +4120,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4072,7 +4168,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4192,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>38.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4206,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4216,10 @@
         <v>37.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,14 +4229,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>9</t>
@@ -4158,12 +4254,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -4308,8 +4404,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4348,7 +4452,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4476,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.6</v>
+        <v>37.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4490,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4500,10 @@
         <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -4409,14 +4513,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>8</t>
@@ -4434,12 +4538,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -4584,8 +4688,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4624,7 +4736,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4648,7 +4760,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>34.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4672,7 +4784,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
@@ -4860,8 +4972,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4900,7 +5020,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +5044,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>26.9</v>
+        <v>30</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4948,7 +5068,7 @@
         <v>0.9</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
         <v>71.7</v>
@@ -5136,8 +5256,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -5176,7 +5304,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5328,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.5</v>
+        <v>27.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5352,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -5412,8 +5540,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -5452,7 +5588,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5612,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5500,7 +5636,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -5688,8 +5824,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6054,12 +6198,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6222,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56</v>
+        <v>58.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6236,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6246,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,14 +6259,14 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>5</t>
@@ -6140,12 +6284,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -6290,8 +6434,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6305,12 +6457,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6330,12 +6482,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,7 +6506,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,40 +6520,40 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -6416,12 +6568,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -6443,22 +6595,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -6468,72 +6620,72 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -6566,8 +6718,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6581,12 +6741,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6606,12 +6766,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6630,7 +6790,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>54.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,40 +6804,40 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -6692,12 +6852,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -6719,22 +6879,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -6744,72 +6904,72 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -6842,8 +7002,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6857,12 +7025,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6882,12 +7050,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6906,7 +7074,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.1</v>
+        <v>50.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,40 +7088,40 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -6968,12 +7136,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -6995,22 +7163,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -7025,67 +7193,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -7118,8 +7286,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7133,12 +7309,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7158,12 +7334,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,7 +7358,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,40 +7372,40 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7244,12 +7420,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -7271,27 +7447,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,67 +7477,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7394,8 +7570,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7409,12 +7593,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7434,12 +7618,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7458,7 +7642,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.1</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,40 +7656,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7520,12 +7704,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -7552,22 +7736,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,67 +7761,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -7670,8 +7854,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7710,7 +7902,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7926,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>46.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7758,7 +7950,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
         <v>88.7</v>
@@ -7946,8 +8138,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7961,24 +8161,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -7986,22 +8186,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8010,7 +8210,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.8</v>
+        <v>46.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,40 +8224,40 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8072,12 +8272,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -8099,12 +8299,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -8114,12 +8314,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,101 +8329,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8237,24 +8445,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -8262,22 +8470,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8286,7 +8494,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.8</v>
+        <v>43.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,26 +8508,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>33.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8333,7 +8541,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8375,12 +8583,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8390,12 +8598,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,101 +8613,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8538,7 +8754,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8778,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.2</v>
+        <v>42.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8586,7 +8802,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
         <v>92.09999999999999</v>
@@ -8774,8 +8990,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8814,7 +9038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +9062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.2</v>
+        <v>41.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8862,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
         <v>90.40000000000001</v>
@@ -9050,8 +9274,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9090,7 +9322,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9346,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>40.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9138,7 +9370,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
         <v>95.5</v>
@@ -9326,8 +9558,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9366,7 +9606,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9630,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>38.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9644,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9654,10 @@
         <v>37.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,14 +9667,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>9</t>
@@ -9452,12 +9692,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -9602,8 +9842,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9642,7 +9890,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9914,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.6</v>
+        <v>37.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9928,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9938,10 @@
         <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -9703,14 +9951,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>8</t>
@@ -9728,12 +9976,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -9878,8 +10126,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9918,7 +10174,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9942,7 +10198,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>34.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9966,7 +10222,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
@@ -10154,8 +10410,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10194,7 +10458,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10482,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>26.9</v>
+        <v>30</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10242,7 +10506,7 @@
         <v>0.9</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
         <v>71.7</v>
@@ -10430,8 +10694,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10470,7 +10742,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10766,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.5</v>
+        <v>27.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10518,7 +10790,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -10706,8 +10978,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10746,7 +11026,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +11050,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10794,7 +11074,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -10982,8 +11262,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
